--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484798_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484798_PROCESSED_CHRONO.xlsx
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.8683</v>
+        <v>-0.7179</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0142</v>
+        <v>0.0832</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8541</v>
+        <v>-0.8012</v>
       </c>
       <c r="G3" t="n">
         <v>-0.9036</v>
@@ -688,13 +688,13 @@
         <v>0.1887</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1534</v>
+        <v>-0.0031</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1176</v>
+        <v>-0.0201</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0359</v>
+        <v>0.0171</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.1458</v>
+        <v>-0.898</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6474</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.7931</v>
+        <v>-1.7402</v>
       </c>
       <c r="G4" t="n">
         <v>-0.5729</v>
@@ -766,13 +766,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.271</v>
+        <v>-0.0232</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1764</v>
+        <v>0.0185</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0946</v>
+        <v>-0.0417</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3018</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. GILABERT FERRI</t>
+          <t>I. ALAMINOS HERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.7586</v>
+        <v>-2.1674</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0095</v>
+        <v>-0.4759</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7492</v>
+        <v>-1.6915</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.9744</v>
+        <v>-2.3414</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.4855</v>
+        <v>-1.0056</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5111</v>
+        <v>-1.3357</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1277</v>
+        <v>-0.2407</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.5261</v>
+        <v>-0.2904</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3984</v>
+        <v>0.0496</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8467</v>
+        <v>-2.1007</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9595</v>
+        <v>-0.7153</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8873</v>
+        <v>-1.3854</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1887</v>
+        <v>0.1887</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7548</v>
+        <v>0.1887</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4045</v>
+        <v>-0.0147</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0617</v>
+        <v>-0.2352</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3428</v>
+        <v>0.2205</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. ALAMINOS HERNANDEZ</t>
+          <t>C. GILABERT FERRI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.2996</v>
+        <v>-2.4561</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4759</v>
+        <v>-1.2043</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.8238</v>
+        <v>-1.2518</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.3414</v>
+        <v>-1.9744</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.0056</v>
+        <v>-2.4855</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.3357</v>
+        <v>0.5111</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2407</v>
+        <v>-0.1277</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2904</v>
+        <v>-1.5261</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0496</v>
+        <v>1.3984</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.1007</v>
+        <v>-1.8467</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7153</v>
+        <v>-0.9595</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.3854</v>
+        <v>-0.8873</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1887</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1887</v>
+        <v>0.7548</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.147</v>
+        <v>-0.293</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2352</v>
+        <v>-0.1332</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0882</v>
+        <v>-0.1598</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.189</v>
+        <v>-2.8438</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6137</v>
+        <v>-0.3214</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.5753</v>
+        <v>-2.5224</v>
       </c>
       <c r="G7" t="n">
         <v>-1.6375</v>
@@ -1000,13 +1000,13 @@
         <v>1.1322</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1557</v>
+        <v>-0.8105</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.823</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3327</v>
+        <v>-0.2798</v>
       </c>
       <c r="V7" t="n">
         <v>-1.528</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.162</v>
+        <v>-4.5324</v>
       </c>
       <c r="E8" t="n">
         <v>-0.2419</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.9201</v>
+        <v>-4.2905</v>
       </c>
       <c r="G8" t="n">
         <v>0.6541</v>
@@ -1078,13 +1078,13 @@
         <v>1.3209</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1276</v>
+        <v>-0.2428</v>
       </c>
       <c r="T8" t="n">
         <v>-0.5262</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6538</v>
+        <v>0.2834</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6036</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.3247</v>
+        <v>-5.077</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1835</v>
+        <v>-1.9886</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.1413</v>
+        <v>-3.0883</v>
       </c>
       <c r="G9" t="n">
         <v>-3.2422</v>
@@ -1156,13 +1156,13 @@
         <v>0.7548</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5919</v>
+        <v>-1.3441</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2345</v>
+        <v>-1.0397</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3574</v>
+        <v>-0.3045</v>
       </c>
       <c r="V9" t="n">
         <v>0.6415999999999999</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. FERNANDEZ CARRASCO</t>
+          <t>A. QUERALT-LORTZING VILLANUEVA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.9808</v>
+        <v>-6.3417</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8162</v>
+        <v>-6.2694</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.1645</v>
+        <v>-0.0723</v>
       </c>
       <c r="G10" t="n">
-        <v>-6.399</v>
+        <v>-1.6536</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.2362</v>
+        <v>-1.1535</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.1629</v>
+        <v>-0.5001</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7122000000000001</v>
+        <v>-1.258</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.8867</v>
+        <v>-0.6496</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1745</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-5.6868</v>
+        <v>-0.3956</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.3495</v>
+        <v>-0.504</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.3374</v>
+        <v>0.1083</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9435</v>
+        <v>-4.3401</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9435</v>
+        <v>-4.7175</v>
       </c>
       <c r="R10" t="n">
-        <v>1.887</v>
+        <v>0.3774</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2234</v>
+        <v>-0.348</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4057</v>
+        <v>-0.2939</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1823</v>
+        <v>-0.0541</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. QUERALT-LORTZING VILLANUEVA</t>
+          <t>M. FERNANDEZ CARRASCO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.2888</v>
+        <v>-6.8215</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.2694</v>
+        <v>-1.4983</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0194</v>
+        <v>-5.3233</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.6536</v>
+        <v>-6.399</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1535</v>
+        <v>-4.2362</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5001</v>
+        <v>-2.1629</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.258</v>
+        <v>-0.7122000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6496</v>
+        <v>-0.8867</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6084000000000001</v>
+        <v>0.1745</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3956</v>
+        <v>-5.6868</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.504</v>
+        <v>-3.3495</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1083</v>
+        <v>-2.3374</v>
       </c>
       <c r="P11" t="n">
-        <v>-4.3401</v>
+        <v>0.9435</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.7175</v>
+        <v>-0.9435</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3774</v>
+        <v>1.887</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2951</v>
+        <v>-1.0642</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2939</v>
+        <v>-1.0878</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0012</v>
+        <v>0.0236</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.4689</v>
+        <v>-7.036</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5673</v>
+        <v>-2.3725</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.9016</v>
+        <v>-4.6635</v>
       </c>
       <c r="G12" t="n">
         <v>-3.4047</v>
@@ -1390,13 +1390,13 @@
         <v>0.7548</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.385</v>
+        <v>-0.952</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.823</v>
+        <v>-0.6282</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-0.3239</v>
       </c>
       <c r="V12" t="n">
         <v>-1.547</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.238899999999999</v>
+        <v>-8.4254</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.0742</v>
+        <v>-4.3665</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.1647</v>
+        <v>-4.0588</v>
       </c>
       <c r="G13" t="n">
         <v>-4.8144</v>
@@ -1468,13 +1468,13 @@
         <v>0.7548</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4244</v>
+        <v>-0.6109</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.291</v>
+        <v>-0.5833</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1334</v>
+        <v>-0.0276</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9244</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-11.5405</v>
+        <v>-10.9489</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.7266</v>
+        <v>-4.5318</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.8139</v>
+        <v>-6.4171</v>
       </c>
       <c r="G14" t="n">
         <v>-2.2499</v>
@@ -1546,13 +1546,13 @@
         <v>1.3209</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.1392</v>
+        <v>-1.5475</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2933</v>
+        <v>-1.0985</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8459</v>
+        <v>-0.4491</v>
       </c>
       <c r="V14" t="n">
         <v>-1.8678</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-56.3981</v>
+        <v>-56.3983</v>
       </c>
       <c r="E15" t="n">
-        <v>-20.4772</v>
+        <v>-20.4774</v>
       </c>
       <c r="F15" t="n">
-        <v>-35.921</v>
+        <v>-35.9209</v>
       </c>
       <c r="G15" t="n">
         <v>-26.6717</v>
@@ -1594,10 +1594,10 @@
         <v>-21.6935</v>
       </c>
       <c r="I15" t="n">
-        <v>-4.978299999999999</v>
+        <v>-4.9783</v>
       </c>
       <c r="J15" t="n">
-        <v>9.9102</v>
+        <v>9.910199999999998</v>
       </c>
       <c r="K15" t="n">
         <v>-2.4263</v>
@@ -1624,13 +1624,13 @@
         <v>9.435</v>
       </c>
       <c r="S15" t="n">
-        <v>-7.254000000000001</v>
+        <v>-7.254</v>
       </c>
       <c r="T15" t="n">
-        <v>-6.158100000000001</v>
+        <v>-6.158300000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.096</v>
+        <v>-1.0959</v>
       </c>
       <c r="V15" t="n">
         <v>-6.4328</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>9.5701</v>
+        <v>10.0476</v>
       </c>
       <c r="E16" t="n">
-        <v>10.386</v>
+        <v>10.6783</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8158</v>
+        <v>-0.6307</v>
       </c>
       <c r="G16" t="n">
         <v>7.1789</v>
@@ -1702,13 +1702,13 @@
         <v>2.6418</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0893</v>
+        <v>0.5668</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0276</v>
+        <v>0.3199</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0618</v>
+        <v>0.2469</v>
       </c>
       <c r="V16" t="n">
         <v>0.6036</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>7.0693</v>
+        <v>7.8126</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2699</v>
+        <v>2.8545</v>
       </c>
       <c r="F17" t="n">
-        <v>4.7994</v>
+        <v>4.9581</v>
       </c>
       <c r="G17" t="n">
         <v>3.3194</v>
@@ -1780,13 +1780,13 @@
         <v>3.774</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0241</v>
+        <v>0.7192</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8818</v>
+        <v>-0.2972</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8577</v>
+        <v>1.0164</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>6.6881</v>
+        <v>7.1837</v>
       </c>
       <c r="E18" t="n">
-        <v>4.9545</v>
+        <v>5.3443</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7336</v>
+        <v>1.8394</v>
       </c>
       <c r="G18" t="n">
         <v>2.5066</v>
@@ -1858,13 +1858,13 @@
         <v>1.6983</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0118</v>
+        <v>0.5073</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3868</v>
+        <v>0.0029</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3986</v>
+        <v>0.5044</v>
       </c>
       <c r="V18" t="n">
         <v>2.4714</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>5.4685</v>
+        <v>5.6898</v>
       </c>
       <c r="E19" t="n">
-        <v>4.5808</v>
+        <v>4.7757</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8875999999999999</v>
+        <v>0.9141</v>
       </c>
       <c r="G19" t="n">
         <v>2.8971</v>
@@ -1936,13 +1936,13 @@
         <v>1.1322</v>
       </c>
       <c r="S19" t="n">
-        <v>0.194</v>
+        <v>0.4153</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1517</v>
+        <v>0.0432</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3457</v>
+        <v>0.3721</v>
       </c>
       <c r="V19" t="n">
         <v>1.2452</v>
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>5.0094</v>
+        <v>5.3991</v>
       </c>
       <c r="E20" t="n">
-        <v>2.858</v>
+        <v>3.2478</v>
       </c>
       <c r="F20" t="n">
         <v>2.1513</v>
@@ -2014,10 +2014,10 @@
         <v>3.2079</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6249</v>
+        <v>1.0146</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0029</v>
+        <v>0.3926</v>
       </c>
       <c r="U20" t="n">
         <v>0.622</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. MARCO CLIMENT</t>
+          <t>V. SANTAMATILDE PERIS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>4.6373</v>
+        <v>4.7191</v>
       </c>
       <c r="E21" t="n">
-        <v>2.6066</v>
+        <v>2.2219</v>
       </c>
       <c r="F21" t="n">
-        <v>2.0306</v>
+        <v>2.4972</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5615</v>
+        <v>0.6324</v>
       </c>
       <c r="H21" t="n">
-        <v>2.3431</v>
+        <v>0.9008</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.7816</v>
+        <v>-0.2683</v>
       </c>
       <c r="J21" t="n">
-        <v>1.8287</v>
+        <v>2.0997</v>
       </c>
       <c r="K21" t="n">
-        <v>2.1819</v>
+        <v>0.5283</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.3531</v>
+        <v>1.5715</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2673</v>
+        <v>-1.4673</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1612</v>
+        <v>0.3725</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.4285</v>
+        <v>-1.8398</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2644</v>
+        <v>3.2079</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.2644</v>
+        <v>3.2079</v>
       </c>
       <c r="S21" t="n">
-        <v>1.5096</v>
+        <v>0.577</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4761</v>
+        <v>-0.1796</v>
       </c>
       <c r="U21" t="n">
-        <v>1.0335</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>0.3018</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>V. SANTAMATILDE PERIS</t>
+          <t>A. LÓPEZ ÁLVAREZ-TIRADOR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>4.5049</v>
+        <v>4.0356</v>
       </c>
       <c r="E22" t="n">
-        <v>1.6373</v>
+        <v>4.0356</v>
       </c>
       <c r="F22" t="n">
-        <v>2.8676</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6324</v>
+        <v>4.0356</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9008</v>
+        <v>0.9509</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2683</v>
+        <v>3.0848</v>
       </c>
       <c r="J22" t="n">
-        <v>2.0997</v>
+        <v>4.0356</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5283</v>
+        <v>0.9509</v>
       </c>
       <c r="L22" t="n">
-        <v>1.5715</v>
+        <v>3.0848</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4673</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3725</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.8398</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>3.2079</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>3.2079</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3627</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7642</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.127</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. LÓPEZ ÁLVAREZ-TIRADOR</t>
+          <t>F. MARCO CLIMENT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>4.0356</v>
+        <v>3.7881</v>
       </c>
       <c r="E23" t="n">
-        <v>4.0356</v>
+        <v>2.022</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1.7661</v>
       </c>
       <c r="G23" t="n">
-        <v>4.0356</v>
+        <v>0.5615</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9509</v>
+        <v>2.3431</v>
       </c>
       <c r="I23" t="n">
-        <v>3.0848</v>
+        <v>-1.7816</v>
       </c>
       <c r="J23" t="n">
-        <v>4.0356</v>
+        <v>1.8287</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9509</v>
+        <v>2.1819</v>
       </c>
       <c r="L23" t="n">
-        <v>3.0848</v>
+        <v>-0.3531</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>-1.2673</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>0.1612</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>-1.4285</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.2644</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.2644</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>0.6604</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>-0.1085</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>0.769</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. FAYE</t>
+          <t>D. MARTINEZ JURADO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>3.424</v>
+        <v>2.7812</v>
       </c>
       <c r="E24" t="n">
-        <v>2.8129</v>
+        <v>-0.4073</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6111</v>
+        <v>3.1885</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1186</v>
+        <v>1.8462</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9086</v>
+        <v>2.8745</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.79</v>
+        <v>-1.0283</v>
       </c>
       <c r="J24" t="n">
-        <v>1.3099</v>
+        <v>1.2942</v>
       </c>
       <c r="K24" t="n">
-        <v>1.1042</v>
+        <v>2.3877</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2057</v>
+        <v>-1.0935</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.1913</v>
+        <v>0.552</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1956</v>
+        <v>0.4868</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.9956</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>0.5661</v>
+        <v>0.1887</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5096</v>
+        <v>2.0757</v>
       </c>
       <c r="S24" t="n">
-        <v>2.7393</v>
+        <v>0.7463</v>
       </c>
       <c r="T24" t="n">
-        <v>2.4466</v>
+        <v>0.1854</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2928</v>
+        <v>0.5608</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>D. MARTINEZ JURADO</t>
+          <t>P. ANTICH MINGUEZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,64 +2359,64 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>3.1277</v>
+        <v>2.0881</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1773</v>
+        <v>1.0316</v>
       </c>
       <c r="F25" t="n">
-        <v>2.9505</v>
+        <v>1.0565</v>
       </c>
       <c r="G25" t="n">
-        <v>1.8462</v>
+        <v>1.8721</v>
       </c>
       <c r="H25" t="n">
-        <v>2.8745</v>
+        <v>2.7986</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.0283</v>
+        <v>-0.9264</v>
       </c>
       <c r="J25" t="n">
-        <v>1.2942</v>
+        <v>4.7361</v>
       </c>
       <c r="K25" t="n">
-        <v>2.3877</v>
+        <v>3.2384</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.0935</v>
+        <v>1.4977</v>
       </c>
       <c r="M25" t="n">
-        <v>0.552</v>
+        <v>-2.8639</v>
       </c>
       <c r="N25" t="n">
-        <v>0.4868</v>
+        <v>-0.4398</v>
       </c>
       <c r="O25" t="n">
-        <v>0.06519999999999999</v>
+        <v>-2.4241</v>
       </c>
       <c r="P25" t="n">
-        <v>0.1887</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.887</v>
+        <v>-3.774</v>
       </c>
       <c r="R25" t="n">
-        <v>2.0757</v>
+        <v>3.3966</v>
       </c>
       <c r="S25" t="n">
-        <v>1.0928</v>
+        <v>0.2916</v>
       </c>
       <c r="T25" t="n">
-        <v>0.77</v>
+        <v>-0.2323</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3228</v>
+        <v>0.5238</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>P. ANTICH MINGUEZ</t>
+          <t>P. FAYE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,64 +2437,64 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>1.7778</v>
+        <v>2.007</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6419</v>
+        <v>1.4489</v>
       </c>
       <c r="F26" t="n">
-        <v>1.1358</v>
+        <v>0.5582</v>
       </c>
       <c r="G26" t="n">
-        <v>1.8721</v>
+        <v>0.1186</v>
       </c>
       <c r="H26" t="n">
-        <v>2.7986</v>
+        <v>0.9086</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.9264</v>
+        <v>-0.79</v>
       </c>
       <c r="J26" t="n">
-        <v>4.7361</v>
+        <v>1.3099</v>
       </c>
       <c r="K26" t="n">
-        <v>3.2384</v>
+        <v>1.1042</v>
       </c>
       <c r="L26" t="n">
-        <v>1.4977</v>
+        <v>0.2057</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.8639</v>
+        <v>-1.1913</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.4398</v>
+        <v>-0.1956</v>
       </c>
       <c r="O26" t="n">
-        <v>-2.4241</v>
+        <v>-0.9956</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.3774</v>
+        <v>0.5661</v>
       </c>
       <c r="Q26" t="n">
-        <v>-3.774</v>
+        <v>-0.9435</v>
       </c>
       <c r="R26" t="n">
-        <v>3.3966</v>
+        <v>1.5096</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.0188</v>
+        <v>1.3223</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.622</v>
+        <v>1.0825</v>
       </c>
       <c r="U26" t="n">
-        <v>0.6032</v>
+        <v>0.2399</v>
       </c>
       <c r="V26" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>1.0856</v>
+        <v>0.8462</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.04</v>
+        <v>-1.3323</v>
       </c>
       <c r="F27" t="n">
-        <v>2.1256</v>
+        <v>2.1785</v>
       </c>
       <c r="G27" t="n">
         <v>0.4886</v>
@@ -2560,13 +2560,13 @@
         <v>0.5661</v>
       </c>
       <c r="S27" t="n">
-        <v>0.6725</v>
+        <v>0.4331</v>
       </c>
       <c r="T27" t="n">
-        <v>0.1793</v>
+        <v>-0.113</v>
       </c>
       <c r="U27" t="n">
-        <v>0.4932</v>
+        <v>0.5461</v>
       </c>
       <c r="V27" t="n">
         <v>-0.6415999999999999</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>56.39829999999999</v>
+        <v>56.3981</v>
       </c>
       <c r="E28" t="n">
-        <v>35.9208</v>
+        <v>35.92099999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>20.4773</v>
+        <v>20.4772</v>
       </c>
       <c r="G28" t="n">
         <v>26.6718</v>
@@ -2611,7 +2611,7 @@
         <v>4.9784</v>
       </c>
       <c r="J28" t="n">
-        <v>36.5818</v>
+        <v>36.58179999999999</v>
       </c>
       <c r="K28" t="n">
         <v>19.2676</v>
@@ -2620,7 +2620,7 @@
         <v>17.3147</v>
       </c>
       <c r="M28" t="n">
-        <v>-9.910100000000002</v>
+        <v>-9.9101</v>
       </c>
       <c r="N28" t="n">
         <v>2.4262</v>
@@ -2638,13 +2638,13 @@
         <v>25.4745</v>
       </c>
       <c r="S28" t="n">
-        <v>7.254000000000001</v>
+        <v>7.253899999999999</v>
       </c>
       <c r="T28" t="n">
-        <v>1.096</v>
+        <v>1.0959</v>
       </c>
       <c r="U28" t="n">
-        <v>6.1583</v>
+        <v>6.158</v>
       </c>
       <c r="V28" t="n">
         <v>6.4328</v>
